--- a/artfynd/A 10848-2025 artfynd.xlsx
+++ b/artfynd/A 10848-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,50 +675,53 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>108409807</v>
+        <v>108409784</v>
       </c>
       <c r="B2" t="n">
-        <v>56540</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Skaten, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>669084.0876556924</v>
+        <v>669152</v>
       </c>
       <c r="R2" t="n">
-        <v>6707005.530315585</v>
+        <v>6706913</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -748,19 +751,14 @@
           <t>2023-04-23</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2023-04-23</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Eventuellt natträd</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,50 +785,53 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>108409806</v>
+        <v>108409791</v>
       </c>
       <c r="B3" t="n">
-        <v>56540</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Skaten, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>669083.0542504245</v>
+        <v>669131</v>
       </c>
       <c r="R3" t="n">
-        <v>6707006.469879689</v>
+        <v>6706898</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -860,19 +861,9 @@
           <t>2023-04-23</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2023-04-23</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -896,6 +887,923 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>108409794</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Skaten, Upl</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>669084</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6707008</v>
+      </c>
+      <c r="S4" t="n">
+        <v>15</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Hållnäs</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2023-04-23</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2023-04-23</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Isac Carlsson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Isac Carlsson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>108415163</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>..., Upl</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>669153</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6706888</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Hållnäs</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2023-04-23</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2023-04-23</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Signe Propst</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Signe Propst</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>108415164</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>..., Upl</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>669151</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6706921</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Hållnäs</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2023-04-23</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2023-04-23</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Signe Propst</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Signe Propst</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>108415165</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>..., Upl</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>669046</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6706973</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Hållnäs</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2023-04-23</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2023-04-23</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Signe Propst</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Signe Propst</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>108424220</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Skaten, Upl</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>669032</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6706969</v>
+      </c>
+      <c r="S8" t="n">
+        <v>15</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Hållnäs</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2023-04-23</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2023-04-23</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Ivar Anderberg</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Ivar Anderberg</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>108409806</v>
+      </c>
+      <c r="B9" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Skaten, Upl</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>669083</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6707006</v>
+      </c>
+      <c r="S9" t="n">
+        <v>15</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Hållnäs</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2023-04-23</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2023-04-23</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Isac Carlsson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Isac Carlsson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>108409807</v>
+      </c>
+      <c r="B10" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Skaten, Upl</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>669084</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6707005</v>
+      </c>
+      <c r="S10" t="n">
+        <v>15</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Hållnäs</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2023-04-23</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2023-04-23</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Isac Carlsson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Isac Carlsson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>108409846</v>
+      </c>
+      <c r="B11" t="n">
+        <v>58636</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Skaten, Upl</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>669118</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6707040</v>
+      </c>
+      <c r="S11" t="n">
+        <v>15</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Hållnäs</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2023-04-23</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2023-04-23</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Isac Carlsson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Isac Carlsson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>108424278</v>
+      </c>
+      <c r="B12" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Skaten, Upl</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>669209</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6706926</v>
+      </c>
+      <c r="S12" t="n">
+        <v>15</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Hållnäs</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2023-04-23</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2023-04-23</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Ivar Anderberg</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Ivar Anderberg</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 10848-2025 artfynd.xlsx
+++ b/artfynd/A 10848-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AZ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -782,6 +787,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108409784</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -887,6 +897,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108409791</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -992,6 +1007,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108409794</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1097,6 +1117,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108415163</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1202,6 +1227,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108415164</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1307,6 +1337,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108415165</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1412,6 +1447,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108424220</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1509,6 +1549,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108409806</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1606,6 +1651,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108409807</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1707,6 +1757,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108409846</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1804,8 +1859,26 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108424278</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>